--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88274F3A-892B-40C6-912F-0AA9ABCC7A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E752A8-A314-4F86-B46F-7B6E620E56B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
   <si>
     <t>코트</t>
   </si>
@@ -40,55 +40,75 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>정준섭</t>
+  </si>
+  <si>
+    <t>서지영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문정현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김재혁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>이도훈</t>
-  </si>
-  <si>
-    <t>서지영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>박창민</t>
-  </si>
-  <si>
-    <t>이영준</t>
-  </si>
-  <si>
-    <t>문정현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정우용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강경원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이희연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김신정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>서윤식</t>
-  </si>
-  <si>
-    <t>김재현</t>
-  </si>
-  <si>
-    <t>이희연</t>
-  </si>
-  <si>
-    <t>김신정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정준섭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카밀라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>문민영</t>
-  </si>
-  <si>
-    <t>안재현</t>
-  </si>
-  <si>
-    <t>김재혁</t>
-  </si>
-  <si>
-    <t>강경원</t>
-  </si>
-  <si>
-    <t>정지윤</t>
-  </si>
-  <si>
-    <t>정우용</t>
-  </si>
-  <si>
-    <t>카밀라</t>
-  </si>
-  <si>
-    <t>정준섭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -491,16 +511,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -511,16 +531,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -531,16 +551,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -551,16 +571,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -571,16 +591,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -591,16 +611,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -611,16 +631,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -634,10 +654,10 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -651,16 +671,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -671,16 +691,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -691,16 +711,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -711,16 +731,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -731,16 +751,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
         <v>16</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,16 +771,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -771,16 +791,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E752A8-A314-4F86-B46F-7B6E620E56B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B6BE2D-1EFA-4117-9DCB-283ECC527706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>코트</t>
   </si>
@@ -40,22 +40,63 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>문민영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박창민</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>정준섭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정우용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이희연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김신정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이도훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>서지영</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이영준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>문정현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재현</t>
+    <t>강경원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -63,51 +104,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이도훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>안재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박창민</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정우용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강경원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이희연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김신정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서윤식</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정준섭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>카밀라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>문민영</t>
+    <t>이희현</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -511,16 +508,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -531,16 +528,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -551,16 +548,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -571,16 +568,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -591,16 +588,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -611,16 +608,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -631,16 +628,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -651,16 +648,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -671,13 +668,13 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
@@ -691,16 +688,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -711,16 +708,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -731,16 +728,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
         <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -771,16 +768,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,16 +788,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
         <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B6BE2D-1EFA-4117-9DCB-283ECC527706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7061A3A8-05DE-4086-A502-5C034C302D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>코트</t>
   </si>
@@ -48,19 +48,66 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>서지영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>김재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영호</t>
   </si>
   <si>
     <t>박창민</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정준섭</t>
+  </si>
+  <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>한지윤</t>
   </si>
   <si>
     <t>안재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정준섭</t>
+  </si>
+  <si>
+    <t>김신정</t>
+  </si>
+  <si>
+    <t>김재혁</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>이도훈</t>
+  </si>
+  <si>
+    <t>이희연</t>
+  </si>
+  <si>
+    <t>서지영</t>
+  </si>
+  <si>
+    <t>이영준</t>
+  </si>
+  <si>
+    <t>강경원</t>
+  </si>
+  <si>
+    <t>문민영</t>
+  </si>
+  <si>
+    <t>이찬호</t>
+  </si>
+  <si>
+    <t>한지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강경원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -68,7 +115,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>한지윤</t>
+    <t>김신정</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -76,35 +123,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이희연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이영준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김신정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이도훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서지영</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강경원</t>
+    <t>김재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박창민</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>김재혁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이희현</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -508,16 +535,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -528,16 +555,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -548,16 +575,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -568,16 +595,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -588,16 +615,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -608,16 +635,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -628,16 +655,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -648,16 +675,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -668,16 +695,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -708,16 +735,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,16 +755,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,16 +775,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -768,16 +795,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,16 +815,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7061A3A8-05DE-4086-A502-5C034C302D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8176FA-396C-4DBB-8399-61547CDDDBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="19">
   <si>
     <t>코트</t>
   </si>
@@ -40,99 +40,44 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>이영호</t>
+  </si>
+  <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>이도훈</t>
+  </si>
+  <si>
+    <t>서지영</t>
+  </si>
+  <si>
+    <t>이영준</t>
+  </si>
+  <si>
     <t>문민영</t>
+  </si>
+  <si>
+    <t>이찬호</t>
+  </si>
+  <si>
+    <t>문정현</t>
+  </si>
+  <si>
+    <t>서윤식</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>김종욱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>정지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서지영</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재현</t>
-  </si>
-  <si>
-    <t>이영호</t>
-  </si>
-  <si>
-    <t>박창민</t>
-  </si>
-  <si>
-    <t>정준섭</t>
-  </si>
-  <si>
-    <t>정우용</t>
-  </si>
-  <si>
-    <t>한지윤</t>
-  </si>
-  <si>
-    <t>안재현</t>
-  </si>
-  <si>
-    <t>김신정</t>
-  </si>
-  <si>
-    <t>김재혁</t>
-  </si>
-  <si>
-    <t>정지윤</t>
-  </si>
-  <si>
-    <t>이도훈</t>
-  </si>
-  <si>
-    <t>이희연</t>
-  </si>
-  <si>
-    <t>서지영</t>
-  </si>
-  <si>
-    <t>이영준</t>
-  </si>
-  <si>
     <t>강경원</t>
   </si>
   <si>
-    <t>문민영</t>
-  </si>
-  <si>
-    <t>이찬호</t>
-  </si>
-  <si>
-    <t>한지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강경원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정우용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김신정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이영호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박창민</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재혁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>정혜린</t>
   </si>
 </sst>
 </file>
@@ -535,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -555,16 +500,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -575,16 +520,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -595,16 +540,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
       <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -615,16 +560,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
         <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -635,16 +580,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -655,16 +600,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -675,16 +620,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
       <c r="F9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -695,16 +640,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -715,16 +660,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
         <v>17</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -735,16 +680,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -755,16 +700,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -775,16 +720,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -795,13 +740,13 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -815,16 +760,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8176FA-396C-4DBB-8399-61547CDDDBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C7F80B-2346-4A0B-AAA9-D239491B9650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
   <si>
     <t>코트</t>
   </si>
@@ -40,44 +40,58 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>김재혁</t>
+  </si>
+  <si>
+    <t>박창민</t>
+  </si>
+  <si>
     <t>이영호</t>
   </si>
   <si>
-    <t>정우용</t>
-  </si>
-  <si>
-    <t>이도훈</t>
+    <t>김재현</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>서윤식</t>
+  </si>
+  <si>
+    <t>문정현</t>
   </si>
   <si>
     <t>서지영</t>
   </si>
   <si>
+    <t>김신정</t>
+  </si>
+  <si>
+    <t>이찬호</t>
+  </si>
+  <si>
+    <t>한지윤</t>
+  </si>
+  <si>
+    <t>안재현</t>
+  </si>
+  <si>
+    <t>정혜린</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
     <t>이영준</t>
   </si>
   <si>
-    <t>문민영</t>
-  </si>
-  <si>
-    <t>이찬호</t>
-  </si>
-  <si>
-    <t>문정현</t>
-  </si>
-  <si>
-    <t>서윤식</t>
-  </si>
-  <si>
-    <t>김종욱</t>
-  </si>
-  <si>
-    <t>김종욱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강경원</t>
-  </si>
-  <si>
-    <t>정혜린</t>
+    <t>이희연</t>
+  </si>
+  <si>
+    <t>카밀라</t>
   </si>
 </sst>
 </file>
@@ -480,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -500,16 +514,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -520,16 +534,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -540,16 +554,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -560,16 +574,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -580,16 +594,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -600,16 +614,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -620,16 +634,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -640,16 +654,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
         <v>6</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -660,16 +674,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -680,16 +694,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -700,16 +714,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -720,16 +734,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -740,16 +754,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -760,16 +774,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C7F80B-2346-4A0B-AAA9-D239491B9650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA489CF-221E-4A70-AA4F-4E5E88742244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -40,58 +40,76 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>이영호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이희연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이찬호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카밀라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문정현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이도훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김종욱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김재혁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박창민</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>서지영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>정우용</t>
-  </si>
-  <si>
-    <t>김재혁</t>
-  </si>
-  <si>
-    <t>박창민</t>
-  </si>
-  <si>
-    <t>이영호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정혜린</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강경원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>김재현</t>
-  </si>
-  <si>
-    <t>김종욱</t>
-  </si>
-  <si>
-    <t>서윤식</t>
-  </si>
-  <si>
-    <t>문정현</t>
-  </si>
-  <si>
-    <t>서지영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>김신정</t>
-  </si>
-  <si>
-    <t>이찬호</t>
-  </si>
-  <si>
-    <t>한지윤</t>
-  </si>
-  <si>
-    <t>안재현</t>
-  </si>
-  <si>
-    <t>정혜린</t>
-  </si>
-  <si>
-    <t>정지윤</t>
-  </si>
-  <si>
-    <t>이영준</t>
-  </si>
-  <si>
-    <t>이희연</t>
-  </si>
-  <si>
-    <t>카밀라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -494,16 +512,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -514,16 +532,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -534,16 +552,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -554,16 +572,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -574,16 +592,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -594,16 +612,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -614,16 +632,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -634,16 +652,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -654,16 +672,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -674,16 +692,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -694,16 +712,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -714,16 +732,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -734,16 +752,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -754,16 +772,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -780,10 +798,10 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA489CF-221E-4A70-AA4F-4E5E88742244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D6F8A-B0AF-46EE-9191-87AFC33F6C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="21">
   <si>
     <t>코트</t>
   </si>
@@ -40,76 +40,49 @@
     <t>팀2_선수2</t>
   </si>
   <si>
-    <t>이영호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이희연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>서윤식</t>
+  </si>
+  <si>
+    <t>양현철</t>
+  </si>
+  <si>
+    <t>종운동생</t>
+  </si>
+  <si>
+    <t>강경원</t>
+  </si>
+  <si>
+    <t>박종운</t>
+  </si>
+  <si>
+    <t>김양우</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>김재현</t>
+  </si>
+  <si>
+    <t>박창민</t>
   </si>
   <si>
     <t>안재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정우용</t>
   </si>
   <si>
     <t>이영준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이찬호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>카밀라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>문정현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>민규</t>
   </si>
   <si>
     <t>이도훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김종욱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재혁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박창민</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서지영</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정우용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>정혜린</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강경원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김신정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -518,7 +491,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -532,16 +505,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -552,13 +525,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
@@ -572,16 +545,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -592,16 +565,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -612,16 +585,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -632,16 +605,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -652,16 +625,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -672,16 +645,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -692,16 +665,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -712,16 +685,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -732,13 +705,13 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -752,16 +725,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -772,16 +745,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -792,16 +765,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
         <v>7</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D6F8A-B0AF-46EE-9191-87AFC33F6C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144AFFE6-3620-4170-8CC9-C1AF14CC6C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4845" yWindow="2055" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>코트</t>
   </si>
@@ -43,46 +43,55 @@
     <t>서윤식</t>
   </si>
   <si>
-    <t>양현철</t>
-  </si>
-  <si>
-    <t>종운동생</t>
-  </si>
-  <si>
     <t>강경원</t>
   </si>
   <si>
-    <t>박종운</t>
-  </si>
-  <si>
-    <t>김양우</t>
-  </si>
-  <si>
-    <t>김종욱</t>
-  </si>
-  <si>
     <t>김재현</t>
   </si>
   <si>
     <t>박창민</t>
   </si>
   <si>
-    <t>안재현</t>
-  </si>
-  <si>
     <t>정우용</t>
   </si>
   <si>
-    <t>이영준</t>
-  </si>
-  <si>
-    <t>민규</t>
-  </si>
-  <si>
-    <t>이도훈</t>
-  </si>
-  <si>
     <t>정혜린</t>
+  </si>
+  <si>
+    <t>문정현</t>
+  </si>
+  <si>
+    <t>이영호</t>
+  </si>
+  <si>
+    <t>이찬호</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>김신정</t>
+  </si>
+  <si>
+    <t>서지영</t>
+  </si>
+  <si>
+    <t>문민영</t>
+  </si>
+  <si>
+    <t>성주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문민영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까밀라</t>
   </si>
 </sst>
 </file>
@@ -147,11 +156,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -484,16 +494,16 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -504,17 +514,17 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -524,17 +534,17 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -544,17 +554,17 @@
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -564,17 +574,17 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -584,17 +594,17 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -604,17 +614,17 @@
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -624,17 +634,17 @@
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F9" t="s">
-        <v>19</v>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -644,17 +654,17 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -664,17 +674,17 @@
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -684,17 +694,17 @@
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -704,16 +714,16 @@
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -724,17 +734,17 @@
       <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F14" t="s">
-        <v>16</v>
+      <c r="F14" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -744,17 +754,17 @@
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
+      <c r="C15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -764,17 +774,17 @@
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>7</v>
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144AFFE6-3620-4170-8CC9-C1AF14CC6C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9BCCF4-3A3C-4878-B000-A3E1117C2E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="2055" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>코트</t>
   </si>
@@ -40,58 +40,69 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>강경원</t>
+  </si>
+  <si>
+    <t>김재현</t>
+  </si>
+  <si>
+    <t>박창민</t>
+  </si>
+  <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>서지영</t>
+  </si>
+  <si>
     <t>서윤식</t>
   </si>
   <si>
-    <t>강경원</t>
-  </si>
-  <si>
-    <t>김재현</t>
+    <t>이찬호</t>
+  </si>
+  <si>
+    <t>안재현</t>
+  </si>
+  <si>
+    <t>한지윤</t>
+  </si>
+  <si>
+    <t>정준섭</t>
+  </si>
+  <si>
+    <t>굽다님</t>
+  </si>
+  <si>
+    <t>코제로스님</t>
+  </si>
+  <si>
+    <t>테린이312님</t>
+  </si>
+  <si>
+    <t>테린이312(여)님</t>
+  </si>
+  <si>
+    <t>안재현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김종욱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이찬호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>박창민</t>
-  </si>
-  <si>
-    <t>정우용</t>
-  </si>
-  <si>
-    <t>정혜린</t>
-  </si>
-  <si>
-    <t>문정현</t>
-  </si>
-  <si>
-    <t>이영호</t>
-  </si>
-  <si>
-    <t>이찬호</t>
-  </si>
-  <si>
-    <t>정지윤</t>
-  </si>
-  <si>
-    <t>김신정</t>
-  </si>
-  <si>
-    <t>서지영</t>
-  </si>
-  <si>
-    <t>문민영</t>
-  </si>
-  <si>
-    <t>성주</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>문민영</t>
+    <t>정준섭</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>까밀라</t>
   </si>
 </sst>
 </file>
@@ -156,12 +167,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -466,6 +476,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -494,17 +510,17 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -514,17 +530,17 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
+      <c r="F3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -534,17 +550,17 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
+      <c r="F4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -554,17 +570,17 @@
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
         <v>7</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -574,17 +590,17 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -594,17 +610,17 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>22</v>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -614,17 +630,17 @@
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>19</v>
+      <c r="F8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -634,16 +650,16 @@
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -654,17 +670,17 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>7</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -674,17 +690,17 @@
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
         <v>17</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -694,17 +710,17 @@
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
+      <c r="F12" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -714,17 +730,17 @@
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -734,17 +750,17 @@
       <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>7</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -754,17 +770,17 @@
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>21</v>
+      <c r="F15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -774,16 +790,16 @@
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
         <v>9</v>
       </c>
     </row>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9BCCF4-3A3C-4878-B000-A3E1117C2E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57F32E9-2769-4862-8D48-8151A5E4F871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>코트</t>
   </si>
@@ -40,27 +40,12 @@
     <t>팀2_선수2</t>
   </si>
   <si>
-    <t>강경원</t>
-  </si>
-  <si>
-    <t>김재현</t>
-  </si>
-  <si>
     <t>박창민</t>
   </si>
   <si>
-    <t>정우용</t>
-  </si>
-  <si>
-    <t>김종욱</t>
-  </si>
-  <si>
     <t>서지영</t>
   </si>
   <si>
-    <t>서윤식</t>
-  </si>
-  <si>
     <t>이찬호</t>
   </si>
   <si>
@@ -68,40 +53,51 @@
   </si>
   <si>
     <t>한지윤</t>
-  </si>
-  <si>
-    <t>정준섭</t>
-  </si>
-  <si>
-    <t>굽다님</t>
-  </si>
-  <si>
-    <t>코제로스님</t>
-  </si>
-  <si>
-    <t>테린이312님</t>
-  </si>
-  <si>
-    <t>테린이312(여)님</t>
-  </si>
-  <si>
-    <t>안재현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김종욱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>이찬호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>박창민</t>
+    <t>이영호</t>
+  </si>
+  <si>
+    <t>김재혁</t>
+  </si>
+  <si>
+    <t>까밀라</t>
+  </si>
+  <si>
+    <t>김신정</t>
+  </si>
+  <si>
+    <t>정혜린</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>내동생페더러</t>
+  </si>
+  <si>
+    <t>홍현철</t>
+  </si>
+  <si>
+    <t>이휘영</t>
+  </si>
+  <si>
+    <t>이은교</t>
+  </si>
+  <si>
+    <t>홍현철</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>정준섭</t>
+    <t>이영호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>서지영</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -511,13 +507,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -531,16 +527,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -551,16 +547,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -571,16 +567,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -591,16 +587,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -611,16 +607,16 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -631,16 +627,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
         <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -651,16 +647,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -671,16 +667,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
         <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -691,16 +687,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -711,16 +707,16 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -731,16 +727,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,16 +747,16 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -771,13 +767,13 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -791,16 +787,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57F32E9-2769-4862-8D48-8151A5E4F871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A489B7-A904-4B86-B07C-1EB1D64C265D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>코트</t>
   </si>
@@ -43,25 +43,9 @@
     <t>박창민</t>
   </si>
   <si>
-    <t>서지영</t>
-  </si>
-  <si>
-    <t>이찬호</t>
-  </si>
-  <si>
     <t>안재현</t>
   </si>
   <si>
-    <t>한지윤</t>
-  </si>
-  <si>
-    <t>이찬호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이영호</t>
-  </si>
-  <si>
     <t>김재혁</t>
   </si>
   <si>
@@ -71,33 +55,84 @@
     <t>김신정</t>
   </si>
   <si>
-    <t>정혜린</t>
-  </si>
-  <si>
     <t>정지윤</t>
   </si>
   <si>
-    <t>내동생페더러</t>
-  </si>
-  <si>
-    <t>홍현철</t>
-  </si>
-  <si>
     <t>이휘영</t>
   </si>
   <si>
-    <t>이은교</t>
-  </si>
-  <si>
-    <t>홍현철</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이영호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서지영</t>
+    <t>문정현</t>
+  </si>
+  <si>
+    <t>까미게스트</t>
+  </si>
+  <si>
+    <t>이도훈</t>
+  </si>
+  <si>
+    <t>박수현</t>
+  </si>
+  <si>
+    <t>김예진</t>
+  </si>
+  <si>
+    <t>최지원</t>
+  </si>
+  <si>
+    <t>수현남편님</t>
+  </si>
+  <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>김신정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까미게스트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이도훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김재혁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까밀라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문정현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박창민</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김종욱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수현남편님</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -163,11 +198,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -506,17 +542,17 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -526,17 +562,17 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -546,17 +582,17 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -566,17 +602,17 @@
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -586,17 +622,17 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -606,17 +642,17 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -626,17 +662,17 @@
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -646,16 +682,16 @@
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -666,17 +702,17 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>6</v>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -686,17 +722,17 @@
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
-        <v>8</v>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -706,17 +742,17 @@
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -726,17 +762,17 @@
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -746,17 +782,17 @@
       <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>6</v>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -766,17 +802,17 @@
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F15" t="s">
-        <v>15</v>
+      <c r="E15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -786,17 +822,17 @@
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
+      <c r="F16" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/custom.xlsx
+++ b/dataset/custom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A489B7-A904-4B86-B07C-1EB1D64C265D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03A4448-F8C6-4CCB-86A4-EBBD2863C36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매칭결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>코트</t>
   </si>
@@ -40,99 +40,82 @@
     <t>팀2_선수2</t>
   </si>
   <si>
+    <t>까밀라</t>
+  </si>
+  <si>
+    <t>김신정</t>
+  </si>
+  <si>
+    <t>정우용</t>
+  </si>
+  <si>
+    <t>이영준</t>
+  </si>
+  <si>
+    <t>한지윤</t>
+  </si>
+  <si>
+    <t>이영호</t>
+  </si>
+  <si>
+    <t>김재현</t>
+  </si>
+  <si>
+    <t>양다</t>
+  </si>
+  <si>
+    <t>이도훈</t>
+  </si>
+  <si>
+    <t>nats</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이승연</t>
+  </si>
+  <si>
+    <t>김종욱</t>
+  </si>
+  <si>
+    <t>nats여</t>
+  </si>
+  <si>
+    <t>Kwwwws</t>
+  </si>
+  <si>
+    <t>이승연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>양다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>박창민</t>
   </si>
   <si>
-    <t>안재현</t>
-  </si>
-  <si>
-    <t>김재혁</t>
-  </si>
-  <si>
-    <t>까밀라</t>
-  </si>
-  <si>
-    <t>김신정</t>
-  </si>
-  <si>
-    <t>정지윤</t>
-  </si>
-  <si>
-    <t>이휘영</t>
-  </si>
-  <si>
-    <t>문정현</t>
-  </si>
-  <si>
-    <t>까미게스트</t>
-  </si>
-  <si>
-    <t>이도훈</t>
-  </si>
-  <si>
-    <t>박수현</t>
-  </si>
-  <si>
-    <t>김예진</t>
-  </si>
-  <si>
-    <t>최지원</t>
-  </si>
-  <si>
-    <t>수현남편님</t>
-  </si>
-  <si>
-    <t>정우용</t>
-  </si>
-  <si>
-    <t>김종욱</t>
-  </si>
-  <si>
-    <t>김신정</t>
+    <t>필릭스</t>
+  </si>
+  <si>
+    <t>정혜린</t>
+  </si>
+  <si>
+    <t>nats</t>
+  </si>
+  <si>
+    <t>남복</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>박수현</t>
+    <t>여복</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>까미게스트</t>
+    <t>혼복</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이도훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김재혁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>까밀라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>문정현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정지윤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김예진</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박창민</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김종욱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>수현남편님</t>
+    <t>타입</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -194,6 +177,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -203,7 +197,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -506,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
@@ -515,7 +511,7 @@
     <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,305 +530,353 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
+      <c r="C11" t="s">
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
         <v>7</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
